--- a/full/sliding_window_results_window_10.xlsx
+++ b/full/sliding_window_results_window_10.xlsx
@@ -463,13 +463,13 @@
         <v>29.92</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>29.51802670773275</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.92</v>
+        <v>-0.4019732922672468</v>
       </c>
       <c r="E2" t="n">
-        <v>895.2064000000001</v>
+        <v>0.1615825276961694</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.98</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>29.789942127982</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.98</v>
+        <v>-0.1900578720179986</v>
       </c>
       <c r="E3" t="n">
-        <v>898.8004000000001</v>
+        <v>0.03612199471600994</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>30.04</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>30.01810839594576</v>
       </c>
       <c r="D4" t="n">
-        <v>-30.04</v>
+        <v>-0.02189160405424317</v>
       </c>
       <c r="E4" t="n">
-        <v>902.4015999999999</v>
+        <v>0.0004792423280677562</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>30.21</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>30.33414104483045</v>
       </c>
       <c r="D5" t="n">
-        <v>-30.21</v>
+        <v>0.1241410448304521</v>
       </c>
       <c r="E5" t="n">
-        <v>912.6441000000001</v>
+        <v>0.01541099901159631</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.22</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>30.44695441741961</v>
       </c>
       <c r="D6" t="n">
-        <v>-30.22</v>
+        <v>0.2269544174196128</v>
       </c>
       <c r="E6" t="n">
-        <v>913.2483999999999</v>
+        <v>0.05150830758627582</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.38</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30.26487025116176</v>
       </c>
       <c r="D7" t="n">
-        <v>-30.38</v>
+        <v>-0.115129748838239</v>
       </c>
       <c r="E7" t="n">
-        <v>922.9444</v>
+        <v>0.013254859067556</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.44</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30.30002772833511</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.44</v>
+        <v>-0.1399722716648881</v>
       </c>
       <c r="E8" t="n">
-        <v>926.5936</v>
+        <v>0.01959223683502924</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.48</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>30.48236632579598</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.48</v>
+        <v>0.002366325795982505</v>
       </c>
       <c r="E9" t="n">
-        <v>929.0304</v>
+        <v>5.599497772732234e-06</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.69</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>30.62898618471906</v>
       </c>
       <c r="D10" t="n">
-        <v>-30.69</v>
+        <v>-0.06101381528094407</v>
       </c>
       <c r="E10" t="n">
-        <v>941.8761000000001</v>
+        <v>0.003722685655137164</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.75</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>30.18588338749158</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.75</v>
+        <v>-0.5641166125084247</v>
       </c>
       <c r="E11" t="n">
-        <v>945.5625</v>
+        <v>0.3182275525079802</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.94</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30.31240229444805</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.94</v>
+        <v>-0.6275977055519526</v>
       </c>
       <c r="E12" t="n">
-        <v>957.2836000000001</v>
+        <v>0.3938788800140754</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.95</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>30.6685515859415</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.95</v>
+        <v>-0.2814484140584987</v>
       </c>
       <c r="E13" t="n">
-        <v>957.9024999999999</v>
+        <v>0.07921320977604415</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>31.02</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>31.02168174071198</v>
       </c>
       <c r="D14" t="n">
-        <v>-31.02</v>
+        <v>0.001681740711983792</v>
       </c>
       <c r="E14" t="n">
-        <v>962.2404</v>
+        <v>2.828251822343753e-06</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>31.12</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>31.34523840567913</v>
       </c>
       <c r="D15" t="n">
-        <v>-31.12</v>
+        <v>0.225238405679125</v>
       </c>
       <c r="E15" t="n">
-        <v>968.4544000000001</v>
+        <v>0.0507323393928741</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.28</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>31.32977761628349</v>
       </c>
       <c r="D16" t="n">
-        <v>-31.28</v>
+        <v>0.04977761628348887</v>
       </c>
       <c r="E16" t="n">
-        <v>978.4384000000001</v>
+        <v>0.002477811082866256</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.38</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>31.76660192069113</v>
       </c>
       <c r="D17" t="n">
-        <v>-31.38</v>
+        <v>0.3866019206911346</v>
       </c>
       <c r="E17" t="n">
-        <v>984.7044</v>
+        <v>0.1494610450820744</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.58</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>32.07149440212046</v>
       </c>
       <c r="D18" t="n">
-        <v>-31.58</v>
+        <v>0.491494402120459</v>
       </c>
       <c r="E18" t="n">
-        <v>997.2963999999999</v>
+        <v>0.2415667473157475</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.65</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>32.04447878937641</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.65</v>
+        <v>0.3944787893764143</v>
       </c>
       <c r="E19" t="n">
-        <v>1001.7225</v>
+        <v>0.1556135152678815</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.88</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>31.70459556565881</v>
       </c>
       <c r="D20" t="n">
-        <v>-31.88</v>
+        <v>-0.1754044343411856</v>
       </c>
       <c r="E20" t="n">
-        <v>1016.3344</v>
+        <v>0.03076671558655128</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>32.28</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>32.3360231156244</v>
       </c>
       <c r="D21" t="n">
-        <v>-32.28</v>
+        <v>0.05602311562439866</v>
       </c>
       <c r="E21" t="n">
-        <v>1041.9984</v>
+        <v>0.003138589484264741</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>32.45</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>32.29917956816637</v>
       </c>
       <c r="D22" t="n">
-        <v>-32.45</v>
+        <v>-0.1508204318336297</v>
       </c>
       <c r="E22" t="n">
-        <v>1053.0025</v>
+        <v>0.02274680265848254</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.85</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>33.31699750471096</v>
       </c>
       <c r="D23" t="n">
-        <v>-32.85</v>
+        <v>0.4669975047109602</v>
       </c>
       <c r="E23" t="n">
-        <v>1079.1225</v>
+        <v>0.2180866694062633</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.9</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>32.97503252456637</v>
       </c>
       <c r="D24" t="n">
-        <v>-32.9</v>
+        <v>0.07503252456637455</v>
       </c>
       <c r="E24" t="n">
-        <v>1082.41</v>
+        <v>0.0056298797428036</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>33.1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>33.14286805253617</v>
       </c>
       <c r="D25" t="n">
-        <v>-33.1</v>
+        <v>0.04286805253616421</v>
       </c>
       <c r="E25" t="n">
-        <v>1095.61</v>
+        <v>0.001837669928243335</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>33.4</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>33.09659682782137</v>
       </c>
       <c r="D26" t="n">
-        <v>-33.4</v>
+        <v>-0.3034031721786263</v>
       </c>
       <c r="E26" t="n">
-        <v>1115.56</v>
+        <v>0.09205348488805318</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.7</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>33.733575576439</v>
       </c>
       <c r="D27" t="n">
-        <v>-33.7</v>
+        <v>0.03357557643899867</v>
       </c>
       <c r="E27" t="n">
-        <v>1135.69</v>
+        <v>0.001127319333211042</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>34.1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>34.52395447622725</v>
       </c>
       <c r="D28" t="n">
-        <v>-34.1</v>
+        <v>0.4239544762272516</v>
       </c>
       <c r="E28" t="n">
-        <v>1162.81</v>
+        <v>0.1797373979131232</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>34.4</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>34.55653235092028</v>
       </c>
       <c r="D29" t="n">
-        <v>-34.4</v>
+        <v>0.1565323509202798</v>
       </c>
       <c r="E29" t="n">
-        <v>1183.36</v>
+        <v>0.02450237688462963</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.9</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>35.13333827817324</v>
       </c>
       <c r="D30" t="n">
-        <v>-34.9</v>
+        <v>0.2333382781732425</v>
       </c>
       <c r="E30" t="n">
-        <v>1218.01</v>
+        <v>0.05444675206085349</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>35.3</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>34.92158448717328</v>
       </c>
       <c r="D31" t="n">
-        <v>-35.3</v>
+        <v>-0.3784155128267201</v>
       </c>
       <c r="E31" t="n">
-        <v>1246.09</v>
+        <v>0.1431983003479096</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>35.7</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>35.23280952070267</v>
       </c>
       <c r="D32" t="n">
-        <v>-35.7</v>
+        <v>-0.4671904792973365</v>
       </c>
       <c r="E32" t="n">
-        <v>1274.49</v>
+        <v>0.218266943946075</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>36.3</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>36.00392293331047</v>
       </c>
       <c r="D33" t="n">
-        <v>-36.3</v>
+        <v>-0.2960770666895272</v>
       </c>
       <c r="E33" t="n">
-        <v>1317.69</v>
+        <v>0.08766162941947471</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>36.8</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>36.38271371876629</v>
       </c>
       <c r="D34" t="n">
-        <v>-36.8</v>
+        <v>-0.4172862812337073</v>
       </c>
       <c r="E34" t="n">
-        <v>1354.24</v>
+        <v>0.1741278405058566</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>37.3</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>37.41941067871166</v>
       </c>
       <c r="D35" t="n">
-        <v>-37.3</v>
+        <v>0.1194106787116667</v>
       </c>
       <c r="E35" t="n">
-        <v>1391.29</v>
+        <v>0.01425891019038088</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>37.9</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>37.87342213573044</v>
       </c>
       <c r="D36" t="n">
-        <v>-37.9</v>
+        <v>-0.02657786426955511</v>
       </c>
       <c r="E36" t="n">
-        <v>1436.41</v>
+        <v>0.0007063828691308941</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>38.5</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>38.40034623284688</v>
       </c>
       <c r="D37" t="n">
-        <v>-38.5</v>
+        <v>-0.09965376715312146</v>
       </c>
       <c r="E37" t="n">
-        <v>1482.25</v>
+        <v>0.009930873307808551</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>38.9</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>39.26824967697826</v>
       </c>
       <c r="D38" t="n">
-        <v>-38.9</v>
+        <v>0.3682496769782588</v>
       </c>
       <c r="E38" t="n">
-        <v>1513.21</v>
+        <v>0.135607824594592</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>39.4</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>39.99580818383873</v>
       </c>
       <c r="D39" t="n">
-        <v>-39.4</v>
+        <v>0.5958081838387272</v>
       </c>
       <c r="E39" t="n">
-        <v>1552.36</v>
+        <v>0.3549873919292026</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>39.9</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>40.15353084845763</v>
       </c>
       <c r="D40" t="n">
-        <v>-39.9</v>
+        <v>0.2535308484576362</v>
       </c>
       <c r="E40" t="n">
-        <v>1592.01</v>
+        <v>0.06427789111964888</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>40.1</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>39.99429156781264</v>
       </c>
       <c r="D41" t="n">
-        <v>-40.1</v>
+        <v>-0.1057084321873631</v>
       </c>
       <c r="E41" t="n">
-        <v>1608.01</v>
+        <v>0.01117427263551035</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>40.6</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>41.1970682034644</v>
       </c>
       <c r="D42" t="n">
-        <v>-40.6</v>
+        <v>0.5970682034644028</v>
       </c>
       <c r="E42" t="n">
-        <v>1648.36</v>
+        <v>0.3564904395882095</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>41.43450599492073</v>
       </c>
       <c r="D43" t="n">
-        <v>-40.9</v>
+        <v>0.5345059949207354</v>
       </c>
       <c r="E43" t="n">
-        <v>1672.81</v>
+        <v>0.2856966586062052</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>41.2</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>41.18589790951645</v>
       </c>
       <c r="D44" t="n">
-        <v>-41.2</v>
+        <v>-0.01410209048355426</v>
       </c>
       <c r="E44" t="n">
-        <v>1697.44</v>
+        <v>0.0001988689560063517</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>41.5</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>41.07101789536907</v>
       </c>
       <c r="D45" t="n">
-        <v>-41.5</v>
+        <v>-0.4289821046309328</v>
       </c>
       <c r="E45" t="n">
-        <v>1722.25</v>
+        <v>0.1840256460935846</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.8</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>41.55498737686809</v>
       </c>
       <c r="D46" t="n">
-        <v>-41.8</v>
+        <v>-0.2450126231319061</v>
       </c>
       <c r="E46" t="n">
-        <v>1747.24</v>
+        <v>0.06003118549397744</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>42.2</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>42.09600345691913</v>
       </c>
       <c r="D47" t="n">
-        <v>-42.2</v>
+        <v>-0.1039965430808749</v>
       </c>
       <c r="E47" t="n">
-        <v>1780.84</v>
+        <v>0.01081528097277227</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>42.7</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>42.41385264992605</v>
       </c>
       <c r="D48" t="n">
-        <v>-42.7</v>
+        <v>-0.2861473500739535</v>
       </c>
       <c r="E48" t="n">
-        <v>1823.29</v>
+        <v>0.08188030595434571</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>43.7</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>43.66967031332786</v>
       </c>
       <c r="D49" t="n">
-        <v>-43.7</v>
+        <v>-0.03032968667213964</v>
       </c>
       <c r="E49" t="n">
-        <v>1909.69</v>
+        <v>0.0009198898936301651</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>44.2</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>43.9408469767513</v>
       </c>
       <c r="D50" t="n">
-        <v>-44.2</v>
+        <v>-0.2591530232487074</v>
       </c>
       <c r="E50" t="n">
-        <v>1953.64</v>
+        <v>0.06716028945894506</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>45.6</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>45.44306438683569</v>
       </c>
       <c r="D51" t="n">
-        <v>-45.6</v>
+        <v>-0.1569356131643076</v>
       </c>
       <c r="E51" t="n">
-        <v>2079.36</v>
+        <v>0.0246287866792572</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1759.49</v>
+        <v>-0.488767684261834</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>62983.2283</v>
+        <v>4.612971651533983</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1259.664566</v>
+        <v>0.09225943303067967</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_10.xlsx
+++ b/full/sliding_window_results_window_10.xlsx
@@ -463,13 +463,13 @@
         <v>29.92</v>
       </c>
       <c r="C2" t="n">
-        <v>29.51802670773275</v>
+        <v>29.77036393517265</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4019732922672468</v>
+        <v>-0.1496360648273516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1615825276961694</v>
+        <v>0.02239095189701537</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.98</v>
       </c>
       <c r="C3" t="n">
-        <v>29.789942127982</v>
+        <v>29.93755194389306</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1900578720179986</v>
+        <v>-0.04244805610694158</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03612199471600994</v>
+        <v>0.00180183746725806</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>30.04</v>
       </c>
       <c r="C4" t="n">
-        <v>30.01810839594576</v>
+        <v>30.08832918612211</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.02189160405424317</v>
+        <v>0.0483291861221069</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004792423280677562</v>
+        <v>0.002335710231225251</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>30.21</v>
       </c>
       <c r="C5" t="n">
-        <v>30.33414104483045</v>
+        <v>29.96274883677102</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1241410448304521</v>
+        <v>-0.2472511632289773</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01541099901159631</v>
+        <v>0.0611331377180824</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>30.22</v>
       </c>
       <c r="C6" t="n">
-        <v>30.44695441741961</v>
+        <v>30.0218006587115</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2269544174196128</v>
+        <v>-0.1981993412884968</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05150830758627582</v>
+        <v>0.03928297888719404</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>30.38</v>
       </c>
       <c r="C7" t="n">
-        <v>30.26487025116176</v>
+        <v>30.13067183741966</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.115129748838239</v>
+        <v>-0.249328162580337</v>
       </c>
       <c r="E7" t="n">
-        <v>0.013254859067556</v>
+        <v>0.06216453265568694</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.44</v>
       </c>
       <c r="C8" t="n">
-        <v>30.30002772833511</v>
+        <v>30.20228812312554</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1399722716648881</v>
+        <v>-0.2377118768744566</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01959223683502924</v>
+        <v>0.05650693640717682</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.48</v>
       </c>
       <c r="C9" t="n">
-        <v>30.48236632579598</v>
+        <v>30.43090992038943</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002366325795982505</v>
+        <v>-0.04909007961057199</v>
       </c>
       <c r="E9" t="n">
-        <v>5.599497772732234e-06</v>
+        <v>0.002409835916172296</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.69</v>
       </c>
       <c r="C10" t="n">
-        <v>30.62898618471906</v>
+        <v>30.63588282423835</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.06101381528094407</v>
+        <v>-0.05411717576164676</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003722685655137164</v>
+        <v>0.002928668712416968</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.75</v>
       </c>
       <c r="C11" t="n">
-        <v>30.18588338749158</v>
+        <v>30.3197526712338</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5641166125084247</v>
+        <v>-0.4302473287661961</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3182275525079802</v>
+        <v>0.1851127639104472</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.94</v>
       </c>
       <c r="C12" t="n">
-        <v>30.31240229444805</v>
+        <v>30.63669308316505</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6275977055519526</v>
+        <v>-0.3033069168349556</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3938788800140754</v>
+        <v>0.09199508579992667</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.95</v>
       </c>
       <c r="C13" t="n">
-        <v>30.6685515859415</v>
+        <v>30.75001137401982</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2814484140584987</v>
+        <v>-0.1999886259801755</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07921320977604415</v>
+        <v>0.03999545052143854</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>31.02</v>
       </c>
       <c r="C14" t="n">
-        <v>31.02168174071198</v>
+        <v>30.97567368625794</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001681740711983792</v>
+        <v>-0.04432631374206153</v>
       </c>
       <c r="E14" t="n">
-        <v>2.828251822343753e-06</v>
+        <v>0.001964822089959673</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>31.12</v>
       </c>
       <c r="C15" t="n">
-        <v>31.34523840567913</v>
+        <v>31.12451617322112</v>
       </c>
       <c r="D15" t="n">
-        <v>0.225238405679125</v>
+        <v>0.004516173221119857</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0507323393928741</v>
+        <v>2.03958205631601e-05</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>31.28</v>
       </c>
       <c r="C16" t="n">
-        <v>31.32977761628349</v>
+        <v>31.24297179399211</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04977761628348887</v>
+        <v>-0.03702820600789281</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002477811082866256</v>
+        <v>0.001371088040162949</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>31.38</v>
       </c>
       <c r="C17" t="n">
-        <v>31.76660192069113</v>
+        <v>31.32073056535312</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3866019206911346</v>
+        <v>-0.0592694346468754</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1494610450820744</v>
+        <v>0.003512865883360233</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.58</v>
       </c>
       <c r="C18" t="n">
-        <v>32.07149440212046</v>
+        <v>31.5274405053134</v>
       </c>
       <c r="D18" t="n">
-        <v>0.491494402120459</v>
+        <v>-0.05255949468659793</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2415667473157475</v>
+        <v>0.002762500481710516</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.65</v>
       </c>
       <c r="C19" t="n">
-        <v>32.04447878937641</v>
+        <v>31.46250397890954</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3944787893764143</v>
+        <v>-0.1874960210904568</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1556135152678815</v>
+        <v>0.03515475792475303</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.88</v>
       </c>
       <c r="C20" t="n">
-        <v>31.70459556565881</v>
+        <v>31.74143057845111</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1754044343411856</v>
+        <v>-0.138569421548894</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03076671558655128</v>
+        <v>0.01920148458839508</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>32.28</v>
       </c>
       <c r="C21" t="n">
-        <v>32.3360231156244</v>
+        <v>31.96299095044684</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05602311562439866</v>
+        <v>-0.3170090495531639</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003138589484264741</v>
+        <v>0.1004947374986003</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>32.45</v>
       </c>
       <c r="C22" t="n">
-        <v>32.29917956816637</v>
+        <v>32.11835357209749</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1508204318336297</v>
+        <v>-0.3316464279025126</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02274680265848254</v>
+        <v>0.1099893531404965</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>32.85</v>
       </c>
       <c r="C23" t="n">
-        <v>33.31699750471096</v>
+        <v>32.97566046404976</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4669975047109602</v>
+        <v>0.1256604640497585</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2180866694062633</v>
+        <v>0.01579055222520065</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>32.9</v>
       </c>
       <c r="C24" t="n">
-        <v>32.97503252456637</v>
+        <v>32.83036900549757</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07503252456637455</v>
+        <v>-0.06963099450242538</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0056298797428036</v>
+        <v>0.004848475395396794</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>33.1</v>
       </c>
       <c r="C25" t="n">
-        <v>33.14286805253617</v>
+        <v>32.94767017087827</v>
       </c>
       <c r="D25" t="n">
-        <v>0.04286805253616421</v>
+        <v>-0.152329829121733</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001837669928243335</v>
+        <v>0.02320437684025637</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>33.4</v>
       </c>
       <c r="C26" t="n">
-        <v>33.09659682782137</v>
+        <v>33.06243181166948</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3034031721786263</v>
+        <v>-0.3375681883305148</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09205348488805318</v>
+        <v>0.1139522817727459</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>33.7</v>
       </c>
       <c r="C27" t="n">
-        <v>33.733575576439</v>
+        <v>33.49642765291951</v>
       </c>
       <c r="D27" t="n">
-        <v>0.03357557643899867</v>
+        <v>-0.2035723470804953</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001127319333211042</v>
+        <v>0.04144170049586165</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>34.1</v>
       </c>
       <c r="C28" t="n">
-        <v>34.52395447622725</v>
+        <v>34.04124133433146</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4239544762272516</v>
+        <v>-0.05875866566854171</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1797373979131232</v>
+        <v>0.003452580791147462</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>34.4</v>
       </c>
       <c r="C29" t="n">
-        <v>34.55653235092028</v>
+        <v>34.22034084117995</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1565323509202798</v>
+        <v>-0.1796591588200442</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02450237688462963</v>
+        <v>0.03227741334792588</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>34.9</v>
       </c>
       <c r="C30" t="n">
-        <v>35.13333827817324</v>
+        <v>34.90940174493647</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2333382781732425</v>
+        <v>0.009401744936475609</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05444675206085349</v>
+        <v>8.839280785054475e-05</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>35.3</v>
       </c>
       <c r="C31" t="n">
-        <v>34.92158448717328</v>
+        <v>34.81567365564525</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3784155128267201</v>
+        <v>-0.4843263443547485</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1431983003479096</v>
+        <v>0.2345720078360345</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>35.7</v>
       </c>
       <c r="C32" t="n">
-        <v>35.23280952070267</v>
+        <v>35.35984952082337</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4671904792973365</v>
+        <v>-0.3401504791766357</v>
       </c>
       <c r="E32" t="n">
-        <v>0.218266943946075</v>
+        <v>0.1157023484840948</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>36.3</v>
       </c>
       <c r="C33" t="n">
-        <v>36.00392293331047</v>
+        <v>36.12109079211699</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2960770666895272</v>
+        <v>-0.1789092078830095</v>
       </c>
       <c r="E33" t="n">
-        <v>0.08766162941947471</v>
+        <v>0.03200850466532589</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>36.8</v>
       </c>
       <c r="C34" t="n">
-        <v>36.38271371876629</v>
+        <v>36.58843685394302</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4172862812337073</v>
+        <v>-0.2115631460569745</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1741278405058566</v>
+        <v>0.04475896476952471</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>37.3</v>
       </c>
       <c r="C35" t="n">
-        <v>37.41941067871166</v>
+        <v>37.27165482293807</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1194106787116667</v>
+        <v>-0.02834517706192941</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01425891019038088</v>
+        <v>0.0008034490626721289</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>37.9</v>
       </c>
       <c r="C36" t="n">
-        <v>37.87342213573044</v>
+        <v>37.93638881403669</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.02657786426955511</v>
+        <v>0.03638881403669103</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0007063828691308941</v>
+        <v>0.001324145786996882</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>38.5</v>
       </c>
       <c r="C37" t="n">
-        <v>38.40034623284688</v>
+        <v>38.24034459654068</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.09965376715312146</v>
+        <v>-0.2596554034593197</v>
       </c>
       <c r="E37" t="n">
-        <v>0.009930873307808551</v>
+        <v>0.06742092854562209</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>38.9</v>
       </c>
       <c r="C38" t="n">
-        <v>39.26824967697826</v>
+        <v>38.72299994461898</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3682496769782588</v>
+        <v>-0.177000055381022</v>
       </c>
       <c r="E38" t="n">
-        <v>0.135607824594592</v>
+        <v>0.03132901960488487</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>39.4</v>
       </c>
       <c r="C39" t="n">
-        <v>39.99580818383873</v>
+        <v>39.20235593306173</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5958081838387272</v>
+        <v>-0.1976440669382669</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3549873919292026</v>
+        <v>0.03906317719589811</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>39.9</v>
       </c>
       <c r="C40" t="n">
-        <v>40.15353084845763</v>
+        <v>39.43708525221052</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2535308484576362</v>
+        <v>-0.4629147477894833</v>
       </c>
       <c r="E40" t="n">
-        <v>0.06427789111964888</v>
+        <v>0.2142900637210009</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>40.1</v>
       </c>
       <c r="C41" t="n">
-        <v>39.99429156781264</v>
+        <v>40.14722233695235</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1057084321873631</v>
+        <v>0.0472223369523519</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01117427263551035</v>
+        <v>0.002229949107241459</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>40.6</v>
       </c>
       <c r="C42" t="n">
-        <v>41.1970682034644</v>
+        <v>40.44262604342581</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5970682034644028</v>
+        <v>-0.1573739565741903</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3564904395882095</v>
+        <v>0.02476656220781513</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>40.9</v>
       </c>
       <c r="C43" t="n">
-        <v>41.43450599492073</v>
+        <v>40.9644852452612</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5345059949207354</v>
+        <v>0.06448524526120281</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2856966586062052</v>
+        <v>0.004158346856397479</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>41.2</v>
       </c>
       <c r="C44" t="n">
-        <v>41.18589790951645</v>
+        <v>41.37036687089012</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.01410209048355426</v>
+        <v>0.1703668708901134</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0001988689560063517</v>
+        <v>0.02902487069688856</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>41.5</v>
       </c>
       <c r="C45" t="n">
-        <v>41.07101789536907</v>
+        <v>41.16007244426623</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4289821046309328</v>
+        <v>-0.3399275557337731</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1840256460935846</v>
+        <v>0.1155507431471374</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>41.8</v>
       </c>
       <c r="C46" t="n">
-        <v>41.55498737686809</v>
+        <v>41.48862451110055</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2450126231319061</v>
+        <v>-0.3113754888994507</v>
       </c>
       <c r="E46" t="n">
-        <v>0.06003118549397744</v>
+        <v>0.09695469508737192</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>42.2</v>
       </c>
       <c r="C47" t="n">
-        <v>42.09600345691913</v>
+        <v>41.9689648193808</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1039965430808749</v>
+        <v>-0.2310351806192017</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01081528097277227</v>
+        <v>0.05337725468374715</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>42.7</v>
       </c>
       <c r="C48" t="n">
-        <v>42.41385264992605</v>
+        <v>42.65449369828313</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2861473500739535</v>
+        <v>-0.04550630171686976</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08188030595434571</v>
+        <v>0.002070823495946783</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>43.7</v>
       </c>
       <c r="C49" t="n">
-        <v>43.66967031332786</v>
+        <v>43.72299025906754</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.03032968667213964</v>
+        <v>0.02299025906754082</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0009198898936301651</v>
+        <v>0.0005285520119926428</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>44.2</v>
       </c>
       <c r="C50" t="n">
-        <v>43.9408469767513</v>
+        <v>43.73359740221348</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2591530232487074</v>
+        <v>-0.4664025977865265</v>
       </c>
       <c r="E50" t="n">
-        <v>0.06716028945894506</v>
+        <v>0.2175313832220204</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>45.6</v>
       </c>
       <c r="C51" t="n">
-        <v>45.44306438683569</v>
+        <v>45.35571832503029</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1569356131643076</v>
+        <v>-0.244281674969713</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0246287866792572</v>
+        <v>0.0596735367260085</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.488767684261834</v>
+        <v>-7.93779863442607</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>4.612971651533983</v>
+        <v>2.46472499618305</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.09225943303067967</v>
+        <v>0.04929449992366099</v>
       </c>
     </row>
   </sheetData>
